--- a/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20250301_20250901.xlsx
+++ b/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20250301_20250901.xlsx
@@ -613,37 +613,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62.8099173553719</v>
+        <v>58.67768595041323</v>
       </c>
       <c r="C5" t="n">
-        <v>37.1900826446281</v>
+        <v>41.32231404958678</v>
       </c>
       <c r="D5" t="n">
-        <v>63.85774833965776</v>
+        <v>74.53354745652265</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>INE180A01020</t>
+          <t>INE0DYJ01015</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>-25.6198347107438</v>
+        <v>-17.35537190082645</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
-        <v>1602.2</v>
+        <v>753.25</v>
       </c>
       <c r="K5" t="n">
         <v>4</v>
@@ -657,37 +657,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58.67768595041323</v>
+        <v>62.8099173553719</v>
       </c>
       <c r="C6" t="n">
-        <v>41.32231404958678</v>
+        <v>37.1900826446281</v>
       </c>
       <c r="D6" t="n">
-        <v>74.53354745652265</v>
+        <v>63.85774833965776</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>INE0DYJ01015</t>
+          <t>INE180A01020</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G6" t="n">
-        <v>-17.35537190082645</v>
+        <v>-25.6198347107438</v>
       </c>
       <c r="H6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>20</v>
       </c>
       <c r="J6" t="n">
-        <v>753.25</v>
+        <v>1602.2</v>
       </c>
       <c r="K6" t="n">
         <v>5</v>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G9" t="n">
         <v>-17.35537190082645</v>
@@ -816,7 +816,7 @@
         <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J9" t="n">
         <v>856.9</v>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G10" t="n">
         <v>-18.18181818181819</v>
@@ -860,7 +860,7 @@
         <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J10" t="n">
         <v>6946.5</v>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G11" t="n">
         <v>-15.70247933884297</v>
@@ -904,7 +904,7 @@
         <v>14</v>
       </c>
       <c r="I11" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J11" t="n">
         <v>807.1</v>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G12" t="n">
         <v>-14.0495867768595</v>
@@ -948,7 +948,7 @@
         <v>21</v>
       </c>
       <c r="I12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J12" t="n">
         <v>977.2</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G13" t="n">
         <v>-17.35537190082645</v>
@@ -992,7 +992,7 @@
         <v>10</v>
       </c>
       <c r="I13" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J13" t="n">
         <v>230.15</v>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G14" t="n">
         <v>-14.0495867768595</v>
@@ -1036,7 +1036,7 @@
         <v>23</v>
       </c>
       <c r="I14" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J14" t="n">
         <v>1478</v>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G15" t="n">
         <v>-10.74380165289256</v>
@@ -1080,7 +1080,7 @@
         <v>50</v>
       </c>
       <c r="I15" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J15" t="n">
         <v>1919.7</v>
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G16" t="n">
         <v>-14.0495867768595</v>
@@ -1124,7 +1124,7 @@
         <v>25</v>
       </c>
       <c r="I16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J16" t="n">
         <v>7091</v>
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G18" t="n">
         <v>-12.39669421487604</v>
@@ -1212,7 +1212,7 @@
         <v>39</v>
       </c>
       <c r="I18" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J18" t="n">
         <v>217.16</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G19" t="n">
         <v>-10.74380165289256</v>
@@ -1256,7 +1256,7 @@
         <v>55</v>
       </c>
       <c r="I19" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J19" t="n">
         <v>403.85</v>
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G20" t="n">
         <v>-12.39669421487604</v>
@@ -1300,7 +1300,7 @@
         <v>37</v>
       </c>
       <c r="I20" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J20" t="n">
         <v>1800.2</v>
